--- a/dataset/results/alpr_results.xlsx
+++ b/dataset/results/alpr_results.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="134">
   <si>
     <t>Filename</t>
   </si>
@@ -28,6 +28,390 @@
   </si>
   <si>
     <t>Numbers</t>
+  </si>
+  <si>
+    <t>٩ ٨ ٨ ٧</t>
+  </si>
+  <si>
+    <t>Filename</t>
+  </si>
+  <si>
+    <t>1.jpg</t>
+  </si>
+  <si>
+    <t>10.jpg</t>
+  </si>
+  <si>
+    <t>11.jpg</t>
+  </si>
+  <si>
+    <t>12.jpg</t>
+  </si>
+  <si>
+    <t>13.jpg</t>
+  </si>
+  <si>
+    <t>14.jpg</t>
+  </si>
+  <si>
+    <t>15.jpg</t>
+  </si>
+  <si>
+    <t>16.jpg</t>
+  </si>
+  <si>
+    <t>17.jpg</t>
+  </si>
+  <si>
+    <t>18.jpg</t>
+  </si>
+  <si>
+    <t>19.jpg</t>
+  </si>
+  <si>
+    <t>2.jpg</t>
+  </si>
+  <si>
+    <t>20.jpg</t>
+  </si>
+  <si>
+    <t>3.jpg</t>
+  </si>
+  <si>
+    <t>4.jpg</t>
+  </si>
+  <si>
+    <t>5.jpg</t>
+  </si>
+  <si>
+    <t>6.jpg</t>
+  </si>
+  <si>
+    <t>7.jpg</t>
+  </si>
+  <si>
+    <t>8.jpg</t>
+  </si>
+  <si>
+    <t>9.jpg</t>
+  </si>
+  <si>
+    <t>Is_Detected</t>
+  </si>
+  <si>
+    <t>Letters</t>
+  </si>
+  <si>
+    <t>م ط ر</t>
+  </si>
+  <si>
+    <t>ر س م</t>
+  </si>
+  <si>
+    <t>ر ص و</t>
+  </si>
+  <si>
+    <t>ر ع أ</t>
+  </si>
+  <si>
+    <t>ر س ه</t>
+  </si>
+  <si>
+    <t>ر أ د</t>
+  </si>
+  <si>
+    <t>ر ب ط</t>
+  </si>
+  <si>
+    <t>م ن س</t>
+  </si>
+  <si>
+    <t>م ف</t>
+  </si>
+  <si>
+    <t>ب ط ل</t>
+  </si>
+  <si>
+    <t>ي ي ي</t>
+  </si>
+  <si>
+    <t>و و و</t>
+  </si>
+  <si>
+    <t>م ج د</t>
+  </si>
+  <si>
+    <t>ر ن أ</t>
+  </si>
+  <si>
+    <t>ر ف ي</t>
+  </si>
+  <si>
+    <t>أ ن ج</t>
+  </si>
+  <si>
+    <t>أ ف ط</t>
+  </si>
+  <si>
+    <t>ر س ن</t>
+  </si>
+  <si>
+    <t>ر س أ</t>
+  </si>
+  <si>
+    <t>د ب ج</t>
+  </si>
+  <si>
+    <t>Numbers</t>
+  </si>
+  <si>
+    <t>٥ ٥ ٥</t>
+  </si>
+  <si>
+    <t>٧ ٨ ٩ ٧</t>
+  </si>
+  <si>
+    <t>٤ ٩ ٦ ٧</t>
+  </si>
+  <si>
+    <t>٧ ٧ ٢ ٩</t>
+  </si>
+  <si>
+    <t>٢ ١ ٣ ١</t>
+  </si>
+  <si>
+    <t>٢ ٩ ٥ ٣</t>
+  </si>
+  <si>
+    <t>٥ ٨ ٢ ٨</t>
+  </si>
+  <si>
+    <t>٦ ٦ ٦ ٦</t>
+  </si>
+  <si>
+    <t>١ ١</t>
+  </si>
+  <si>
+    <t>٩ ٥ ٩</t>
+  </si>
+  <si>
+    <t>٩ ٩ ٩</t>
+  </si>
+  <si>
+    <t>٦ ٦ ٦ ٦</t>
+  </si>
+  <si>
+    <t>٤ ٤ ٤</t>
+  </si>
+  <si>
+    <t>٨ ٦ ٤ ٨</t>
+  </si>
+  <si>
+    <t>٤ ٩ ٨ ٧</t>
+  </si>
+  <si>
+    <t>٢ ٣ ٥ ٩</t>
+  </si>
+  <si>
+    <t>٤ ٥ ٩ ٥</t>
+  </si>
+  <si>
+    <t>٥ ١ ٥ ٩</t>
+  </si>
+  <si>
+    <t>٢ ٨ ٩ ٥</t>
+  </si>
+  <si>
+    <t>٩ ٨ ٨ ٧</t>
+  </si>
+  <si>
+    <t>Filename</t>
+  </si>
+  <si>
+    <t>1.jpg</t>
+  </si>
+  <si>
+    <t>10.jpg</t>
+  </si>
+  <si>
+    <t>11.jpg</t>
+  </si>
+  <si>
+    <t>12.jpg</t>
+  </si>
+  <si>
+    <t>13.jpg</t>
+  </si>
+  <si>
+    <t>14.jpg</t>
+  </si>
+  <si>
+    <t>15.jpg</t>
+  </si>
+  <si>
+    <t>16.jpg</t>
+  </si>
+  <si>
+    <t>17.jpg</t>
+  </si>
+  <si>
+    <t>18.jpg</t>
+  </si>
+  <si>
+    <t>19.jpg</t>
+  </si>
+  <si>
+    <t>2.jpg</t>
+  </si>
+  <si>
+    <t>20.jpg</t>
+  </si>
+  <si>
+    <t>3.jpg</t>
+  </si>
+  <si>
+    <t>4.jpg</t>
+  </si>
+  <si>
+    <t>5.jpg</t>
+  </si>
+  <si>
+    <t>6.jpg</t>
+  </si>
+  <si>
+    <t>7.jpg</t>
+  </si>
+  <si>
+    <t>8.jpg</t>
+  </si>
+  <si>
+    <t>9.jpg</t>
+  </si>
+  <si>
+    <t>Is_Detected</t>
+  </si>
+  <si>
+    <t>Letters</t>
+  </si>
+  <si>
+    <t>م ط ر</t>
+  </si>
+  <si>
+    <t>ر س م</t>
+  </si>
+  <si>
+    <t>ر ص و</t>
+  </si>
+  <si>
+    <t>ر ع أ</t>
+  </si>
+  <si>
+    <t>ر س ه</t>
+  </si>
+  <si>
+    <t>ر أ د</t>
+  </si>
+  <si>
+    <t>ر ب ط</t>
+  </si>
+  <si>
+    <t>م ن س</t>
+  </si>
+  <si>
+    <t>م ف</t>
+  </si>
+  <si>
+    <t>ب ط ل</t>
+  </si>
+  <si>
+    <t>ي ي ي</t>
+  </si>
+  <si>
+    <t>و و و</t>
+  </si>
+  <si>
+    <t>م ج د</t>
+  </si>
+  <si>
+    <t>ر ن أ</t>
+  </si>
+  <si>
+    <t>ر ف ي</t>
+  </si>
+  <si>
+    <t>أ ن ج</t>
+  </si>
+  <si>
+    <t>أ ف ط</t>
+  </si>
+  <si>
+    <t>ر س ن</t>
+  </si>
+  <si>
+    <t>ر س أ</t>
+  </si>
+  <si>
+    <t>د ب ج</t>
+  </si>
+  <si>
+    <t>Numbers</t>
+  </si>
+  <si>
+    <t>٥ ٥ ٥</t>
+  </si>
+  <si>
+    <t>٧ ٨ ٩ ٧</t>
+  </si>
+  <si>
+    <t>٤ ٩ ٦ ٧</t>
+  </si>
+  <si>
+    <t>٧ ٧ ٢ ٩</t>
+  </si>
+  <si>
+    <t>٢ ١ ٣ ١</t>
+  </si>
+  <si>
+    <t>٢ ٩ ٥ ٣</t>
+  </si>
+  <si>
+    <t>٥ ٨ ٢ ٨</t>
+  </si>
+  <si>
+    <t>٦ ٦ ٦ ٦</t>
+  </si>
+  <si>
+    <t>١ ١</t>
+  </si>
+  <si>
+    <t>٩ ٥ ٩</t>
+  </si>
+  <si>
+    <t>٩ ٩ ٩</t>
+  </si>
+  <si>
+    <t>٦ ٦ ٦ ٦</t>
+  </si>
+  <si>
+    <t>٤ ٤ ٤</t>
+  </si>
+  <si>
+    <t>٨ ٦ ٤ ٨</t>
+  </si>
+  <si>
+    <t>٤ ٩ ٨ ٧</t>
+  </si>
+  <si>
+    <t>٢ ٣ ٥ ٩</t>
+  </si>
+  <si>
+    <t>٤ ٥ ٩ ٥</t>
+  </si>
+  <si>
+    <t>٥ ١ ٥ ٩</t>
+  </si>
+  <si>
+    <t>٢ ٨ ٩ ٥</t>
   </si>
   <si>
     <t>٩ ٨ ٨ ٧</t>
@@ -51,7 +435,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -60,13 +444,17 @@
       <diagonal/>
     </border>
     <border/>
+    <border/>
+    <border/>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="22" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="true"/>
+    <xf numFmtId="22" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="true"/>
+    <xf numFmtId="22" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="true"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -87,180 +475,296 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="0" t="s">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="B1" s="0" t="s">
-        <v>1</v>
+        <v>91</v>
       </c>
       <c r="C1" s="0" t="s">
-        <v>2</v>
+        <v>92</v>
       </c>
       <c r="D1" s="0" t="s">
-        <v>4</v>
+        <v>113</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="0"/>
+      <c r="A2" s="0" t="s">
+        <v>71</v>
+      </c>
       <c r="B2" s="0" t="b">
-        <v>0</v>
-      </c>
-      <c r="C2" s="0"/>
-      <c r="D2" s="0"/>
+        <v>1</v>
+      </c>
+      <c r="C2" s="0" t="s">
+        <v>93</v>
+      </c>
+      <c r="D2" s="0" t="s">
+        <v>114</v>
+      </c>
     </row>
     <row r="3">
-      <c r="A3" s="0"/>
+      <c r="A3" s="0" t="s">
+        <v>72</v>
+      </c>
       <c r="B3" s="0" t="b">
-        <v>0</v>
-      </c>
-      <c r="C3" s="0"/>
-      <c r="D3" s="0"/>
+        <v>1</v>
+      </c>
+      <c r="C3" s="0" t="s">
+        <v>94</v>
+      </c>
+      <c r="D3" s="0" t="s">
+        <v>115</v>
+      </c>
     </row>
     <row r="4">
-      <c r="A4" s="0"/>
+      <c r="A4" s="0" t="s">
+        <v>73</v>
+      </c>
       <c r="B4" s="0" t="b">
-        <v>0</v>
-      </c>
-      <c r="C4" s="0"/>
-      <c r="D4" s="0"/>
+        <v>1</v>
+      </c>
+      <c r="C4" s="0" t="s">
+        <v>95</v>
+      </c>
+      <c r="D4" s="0" t="s">
+        <v>116</v>
+      </c>
     </row>
     <row r="5">
-      <c r="A5" s="0"/>
+      <c r="A5" s="0" t="s">
+        <v>74</v>
+      </c>
       <c r="B5" s="0" t="b">
-        <v>0</v>
-      </c>
-      <c r="C5" s="0"/>
-      <c r="D5" s="0"/>
+        <v>1</v>
+      </c>
+      <c r="C5" s="0" t="s">
+        <v>96</v>
+      </c>
+      <c r="D5" s="0" t="s">
+        <v>117</v>
+      </c>
     </row>
     <row r="6">
-      <c r="A6" s="0"/>
+      <c r="A6" s="0" t="s">
+        <v>75</v>
+      </c>
       <c r="B6" s="0" t="b">
-        <v>0</v>
-      </c>
-      <c r="C6" s="0"/>
-      <c r="D6" s="0"/>
+        <v>1</v>
+      </c>
+      <c r="C6" s="0" t="s">
+        <v>97</v>
+      </c>
+      <c r="D6" s="0" t="s">
+        <v>118</v>
+      </c>
     </row>
     <row r="7">
-      <c r="A7" s="0"/>
+      <c r="A7" s="0" t="s">
+        <v>76</v>
+      </c>
       <c r="B7" s="0" t="b">
-        <v>0</v>
-      </c>
-      <c r="C7" s="0"/>
-      <c r="D7" s="0"/>
+        <v>1</v>
+      </c>
+      <c r="C7" s="0" t="s">
+        <v>98</v>
+      </c>
+      <c r="D7" s="0" t="s">
+        <v>119</v>
+      </c>
     </row>
     <row r="8">
-      <c r="A8" s="0"/>
+      <c r="A8" s="0" t="s">
+        <v>77</v>
+      </c>
       <c r="B8" s="0" t="b">
-        <v>0</v>
-      </c>
-      <c r="C8" s="0"/>
-      <c r="D8" s="0"/>
+        <v>1</v>
+      </c>
+      <c r="C8" s="0" t="s">
+        <v>99</v>
+      </c>
+      <c r="D8" s="0" t="s">
+        <v>120</v>
+      </c>
     </row>
     <row r="9">
-      <c r="A9" s="0"/>
+      <c r="A9" s="0" t="s">
+        <v>78</v>
+      </c>
       <c r="B9" s="0" t="b">
-        <v>0</v>
-      </c>
-      <c r="C9" s="0"/>
-      <c r="D9" s="0"/>
+        <v>1</v>
+      </c>
+      <c r="C9" s="0" t="s">
+        <v>100</v>
+      </c>
+      <c r="D9" s="0" t="s">
+        <v>121</v>
+      </c>
     </row>
     <row r="10">
-      <c r="A10" s="0"/>
+      <c r="A10" s="0" t="s">
+        <v>79</v>
+      </c>
       <c r="B10" s="0" t="b">
-        <v>0</v>
-      </c>
-      <c r="C10" s="0"/>
-      <c r="D10" s="0"/>
+        <v>1</v>
+      </c>
+      <c r="C10" s="0" t="s">
+        <v>101</v>
+      </c>
+      <c r="D10" s="0" t="s">
+        <v>122</v>
+      </c>
     </row>
     <row r="11">
-      <c r="A11" s="0"/>
+      <c r="A11" s="0" t="s">
+        <v>80</v>
+      </c>
       <c r="B11" s="0" t="b">
-        <v>0</v>
-      </c>
-      <c r="C11" s="0"/>
-      <c r="D11" s="0"/>
+        <v>1</v>
+      </c>
+      <c r="C11" s="0" t="s">
+        <v>102</v>
+      </c>
+      <c r="D11" s="0" t="s">
+        <v>123</v>
+      </c>
     </row>
     <row r="12">
-      <c r="A12" s="0"/>
+      <c r="A12" s="0" t="s">
+        <v>81</v>
+      </c>
       <c r="B12" s="0" t="b">
-        <v>0</v>
-      </c>
-      <c r="C12" s="0"/>
-      <c r="D12" s="0"/>
+        <v>1</v>
+      </c>
+      <c r="C12" s="0" t="s">
+        <v>103</v>
+      </c>
+      <c r="D12" s="0" t="s">
+        <v>124</v>
+      </c>
     </row>
     <row r="13">
-      <c r="A13" s="0"/>
+      <c r="A13" s="0" t="s">
+        <v>82</v>
+      </c>
       <c r="B13" s="0" t="b">
-        <v>0</v>
-      </c>
-      <c r="C13" s="0"/>
-      <c r="D13" s="0"/>
+        <v>1</v>
+      </c>
+      <c r="C13" s="0" t="s">
+        <v>104</v>
+      </c>
+      <c r="D13" s="0" t="s">
+        <v>125</v>
+      </c>
     </row>
     <row r="14">
-      <c r="A14" s="0"/>
+      <c r="A14" s="0" t="s">
+        <v>83</v>
+      </c>
       <c r="B14" s="0" t="b">
-        <v>0</v>
-      </c>
-      <c r="C14" s="0"/>
-      <c r="D14" s="0"/>
+        <v>1</v>
+      </c>
+      <c r="C14" s="0" t="s">
+        <v>105</v>
+      </c>
+      <c r="D14" s="0" t="s">
+        <v>126</v>
+      </c>
     </row>
     <row r="15">
-      <c r="A15" s="0"/>
+      <c r="A15" s="0" t="s">
+        <v>84</v>
+      </c>
       <c r="B15" s="0" t="b">
-        <v>0</v>
-      </c>
-      <c r="C15" s="0"/>
-      <c r="D15" s="0"/>
+        <v>1</v>
+      </c>
+      <c r="C15" s="0" t="s">
+        <v>106</v>
+      </c>
+      <c r="D15" s="0" t="s">
+        <v>127</v>
+      </c>
     </row>
     <row r="16">
-      <c r="A16" s="0"/>
+      <c r="A16" s="0" t="s">
+        <v>85</v>
+      </c>
       <c r="B16" s="0" t="b">
-        <v>0</v>
-      </c>
-      <c r="C16" s="0"/>
-      <c r="D16" s="0"/>
+        <v>1</v>
+      </c>
+      <c r="C16" s="0" t="s">
+        <v>107</v>
+      </c>
+      <c r="D16" s="0" t="s">
+        <v>128</v>
+      </c>
     </row>
     <row r="17">
-      <c r="A17" s="0"/>
+      <c r="A17" s="0" t="s">
+        <v>86</v>
+      </c>
       <c r="B17" s="0" t="b">
-        <v>0</v>
-      </c>
-      <c r="C17" s="0"/>
-      <c r="D17" s="0"/>
+        <v>1</v>
+      </c>
+      <c r="C17" s="0" t="s">
+        <v>108</v>
+      </c>
+      <c r="D17" s="0" t="s">
+        <v>129</v>
+      </c>
     </row>
     <row r="18">
-      <c r="A18" s="0"/>
+      <c r="A18" s="0" t="s">
+        <v>87</v>
+      </c>
       <c r="B18" s="0" t="b">
-        <v>0</v>
-      </c>
-      <c r="C18" s="0"/>
-      <c r="D18" s="0"/>
+        <v>1</v>
+      </c>
+      <c r="C18" s="0" t="s">
+        <v>109</v>
+      </c>
+      <c r="D18" s="0" t="s">
+        <v>130</v>
+      </c>
     </row>
     <row r="19">
-      <c r="A19" s="0"/>
+      <c r="A19" s="0" t="s">
+        <v>88</v>
+      </c>
       <c r="B19" s="0" t="b">
-        <v>0</v>
-      </c>
-      <c r="C19" s="0"/>
-      <c r="D19" s="0"/>
+        <v>1</v>
+      </c>
+      <c r="C19" s="0" t="s">
+        <v>110</v>
+      </c>
+      <c r="D19" s="0" t="s">
+        <v>131</v>
+      </c>
     </row>
     <row r="20">
-      <c r="A20" s="0"/>
+      <c r="A20" s="0" t="s">
+        <v>89</v>
+      </c>
       <c r="B20" s="0" t="b">
-        <v>0</v>
-      </c>
-      <c r="C20" s="0"/>
-      <c r="D20" s="0"/>
+        <v>1</v>
+      </c>
+      <c r="C20" s="0" t="s">
+        <v>111</v>
+      </c>
+      <c r="D20" s="0" t="s">
+        <v>132</v>
+      </c>
     </row>
     <row r="21">
-      <c r="A21" s="0"/>
+      <c r="A21" s="0" t="s">
+        <v>90</v>
+      </c>
       <c r="B21" s="0" t="b">
         <v>1</v>
       </c>
       <c r="C21" s="0" t="s">
-        <v>3</v>
+        <v>112</v>
       </c>
       <c r="D21" s="0" t="s">
-        <v>5</v>
+        <v>133</v>
       </c>
     </row>
   </sheetData>

--- a/dataset/results/alpr_results.xlsx
+++ b/dataset/results/alpr_results.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="134">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="390" uniqueCount="390">
   <si>
     <t>Filename</t>
   </si>
@@ -28,6 +28,774 @@
   </si>
   <si>
     <t>Numbers</t>
+  </si>
+  <si>
+    <t>٩ ٨ ٨ ٧</t>
+  </si>
+  <si>
+    <t>Filename</t>
+  </si>
+  <si>
+    <t>1.jpg</t>
+  </si>
+  <si>
+    <t>10.jpg</t>
+  </si>
+  <si>
+    <t>11.jpg</t>
+  </si>
+  <si>
+    <t>12.jpg</t>
+  </si>
+  <si>
+    <t>13.jpg</t>
+  </si>
+  <si>
+    <t>14.jpg</t>
+  </si>
+  <si>
+    <t>15.jpg</t>
+  </si>
+  <si>
+    <t>16.jpg</t>
+  </si>
+  <si>
+    <t>17.jpg</t>
+  </si>
+  <si>
+    <t>18.jpg</t>
+  </si>
+  <si>
+    <t>19.jpg</t>
+  </si>
+  <si>
+    <t>2.jpg</t>
+  </si>
+  <si>
+    <t>20.jpg</t>
+  </si>
+  <si>
+    <t>3.jpg</t>
+  </si>
+  <si>
+    <t>4.jpg</t>
+  </si>
+  <si>
+    <t>5.jpg</t>
+  </si>
+  <si>
+    <t>6.jpg</t>
+  </si>
+  <si>
+    <t>7.jpg</t>
+  </si>
+  <si>
+    <t>8.jpg</t>
+  </si>
+  <si>
+    <t>9.jpg</t>
+  </si>
+  <si>
+    <t>Is_Detected</t>
+  </si>
+  <si>
+    <t>Letters</t>
+  </si>
+  <si>
+    <t>م ط ر</t>
+  </si>
+  <si>
+    <t>ر س م</t>
+  </si>
+  <si>
+    <t>ر ص و</t>
+  </si>
+  <si>
+    <t>ر ع أ</t>
+  </si>
+  <si>
+    <t>ر س ه</t>
+  </si>
+  <si>
+    <t>ر أ د</t>
+  </si>
+  <si>
+    <t>ر ب ط</t>
+  </si>
+  <si>
+    <t>م ن س</t>
+  </si>
+  <si>
+    <t>م ف</t>
+  </si>
+  <si>
+    <t>ب ط ل</t>
+  </si>
+  <si>
+    <t>ي ي ي</t>
+  </si>
+  <si>
+    <t>و و و</t>
+  </si>
+  <si>
+    <t>م ج د</t>
+  </si>
+  <si>
+    <t>ر ن أ</t>
+  </si>
+  <si>
+    <t>ر ف ي</t>
+  </si>
+  <si>
+    <t>أ ن ج</t>
+  </si>
+  <si>
+    <t>أ ف ط</t>
+  </si>
+  <si>
+    <t>ر س ن</t>
+  </si>
+  <si>
+    <t>ر س أ</t>
+  </si>
+  <si>
+    <t>د ب ج</t>
+  </si>
+  <si>
+    <t>Numbers</t>
+  </si>
+  <si>
+    <t>٥ ٥ ٥</t>
+  </si>
+  <si>
+    <t>٧ ٨ ٩ ٧</t>
+  </si>
+  <si>
+    <t>٤ ٩ ٦ ٧</t>
+  </si>
+  <si>
+    <t>٧ ٧ ٢ ٩</t>
+  </si>
+  <si>
+    <t>٢ ١ ٣ ١</t>
+  </si>
+  <si>
+    <t>٢ ٩ ٥ ٣</t>
+  </si>
+  <si>
+    <t>٥ ٨ ٢ ٨</t>
+  </si>
+  <si>
+    <t>٦ ٦ ٦ ٦</t>
+  </si>
+  <si>
+    <t>١ ١</t>
+  </si>
+  <si>
+    <t>٩ ٥ ٩</t>
+  </si>
+  <si>
+    <t>٩ ٩ ٩</t>
+  </si>
+  <si>
+    <t>٦ ٦ ٦ ٦</t>
+  </si>
+  <si>
+    <t>٤ ٤ ٤</t>
+  </si>
+  <si>
+    <t>٨ ٦ ٤ ٨</t>
+  </si>
+  <si>
+    <t>٤ ٩ ٨ ٧</t>
+  </si>
+  <si>
+    <t>٢ ٣ ٥ ٩</t>
+  </si>
+  <si>
+    <t>٤ ٥ ٩ ٥</t>
+  </si>
+  <si>
+    <t>٥ ١ ٥ ٩</t>
+  </si>
+  <si>
+    <t>٢ ٨ ٩ ٥</t>
+  </si>
+  <si>
+    <t>٩ ٨ ٨ ٧</t>
+  </si>
+  <si>
+    <t>Filename</t>
+  </si>
+  <si>
+    <t>1.jpg</t>
+  </si>
+  <si>
+    <t>10.jpg</t>
+  </si>
+  <si>
+    <t>11.jpg</t>
+  </si>
+  <si>
+    <t>12.jpg</t>
+  </si>
+  <si>
+    <t>13.jpg</t>
+  </si>
+  <si>
+    <t>14.jpg</t>
+  </si>
+  <si>
+    <t>15.jpg</t>
+  </si>
+  <si>
+    <t>16.jpg</t>
+  </si>
+  <si>
+    <t>17.jpg</t>
+  </si>
+  <si>
+    <t>18.jpg</t>
+  </si>
+  <si>
+    <t>19.jpg</t>
+  </si>
+  <si>
+    <t>2.jpg</t>
+  </si>
+  <si>
+    <t>20.jpg</t>
+  </si>
+  <si>
+    <t>3.jpg</t>
+  </si>
+  <si>
+    <t>4.jpg</t>
+  </si>
+  <si>
+    <t>5.jpg</t>
+  </si>
+  <si>
+    <t>6.jpg</t>
+  </si>
+  <si>
+    <t>7.jpg</t>
+  </si>
+  <si>
+    <t>8.jpg</t>
+  </si>
+  <si>
+    <t>9.jpg</t>
+  </si>
+  <si>
+    <t>Is_Detected</t>
+  </si>
+  <si>
+    <t>Letters</t>
+  </si>
+  <si>
+    <t>م ط ر</t>
+  </si>
+  <si>
+    <t>ر س م</t>
+  </si>
+  <si>
+    <t>ر ص و</t>
+  </si>
+  <si>
+    <t>ر ع أ</t>
+  </si>
+  <si>
+    <t>ر س ه</t>
+  </si>
+  <si>
+    <t>ر أ د</t>
+  </si>
+  <si>
+    <t>ر ب ط</t>
+  </si>
+  <si>
+    <t>م ن س</t>
+  </si>
+  <si>
+    <t>م ف</t>
+  </si>
+  <si>
+    <t>ب ط ل</t>
+  </si>
+  <si>
+    <t>ي ي ي</t>
+  </si>
+  <si>
+    <t>و و و</t>
+  </si>
+  <si>
+    <t>م ج د</t>
+  </si>
+  <si>
+    <t>ر ن أ</t>
+  </si>
+  <si>
+    <t>ر ف ي</t>
+  </si>
+  <si>
+    <t>أ ن ج</t>
+  </si>
+  <si>
+    <t>أ ف ط</t>
+  </si>
+  <si>
+    <t>ر س ن</t>
+  </si>
+  <si>
+    <t>ر س أ</t>
+  </si>
+  <si>
+    <t>د ب ج</t>
+  </si>
+  <si>
+    <t>Numbers</t>
+  </si>
+  <si>
+    <t>٥ ٥ ٥</t>
+  </si>
+  <si>
+    <t>٧ ٨ ٩ ٧</t>
+  </si>
+  <si>
+    <t>٤ ٩ ٦ ٧</t>
+  </si>
+  <si>
+    <t>٧ ٧ ٢ ٩</t>
+  </si>
+  <si>
+    <t>٢ ١ ٣ ١</t>
+  </si>
+  <si>
+    <t>٢ ٩ ٥ ٣</t>
+  </si>
+  <si>
+    <t>٥ ٨ ٢ ٨</t>
+  </si>
+  <si>
+    <t>٦ ٦ ٦ ٦</t>
+  </si>
+  <si>
+    <t>١ ١</t>
+  </si>
+  <si>
+    <t>٩ ٥ ٩</t>
+  </si>
+  <si>
+    <t>٩ ٩ ٩</t>
+  </si>
+  <si>
+    <t>٦ ٦ ٦ ٦</t>
+  </si>
+  <si>
+    <t>٤ ٤ ٤</t>
+  </si>
+  <si>
+    <t>٨ ٦ ٤ ٨</t>
+  </si>
+  <si>
+    <t>٤ ٩ ٨ ٧</t>
+  </si>
+  <si>
+    <t>٢ ٣ ٥ ٩</t>
+  </si>
+  <si>
+    <t>٤ ٥ ٩ ٥</t>
+  </si>
+  <si>
+    <t>٥ ١ ٥ ٩</t>
+  </si>
+  <si>
+    <t>٢ ٨ ٩ ٥</t>
+  </si>
+  <si>
+    <t>٩ ٨ ٨ ٧</t>
+  </si>
+  <si>
+    <t>Filename</t>
+  </si>
+  <si>
+    <t>1.jpg</t>
+  </si>
+  <si>
+    <t>10.jpg</t>
+  </si>
+  <si>
+    <t>11.jpg</t>
+  </si>
+  <si>
+    <t>12.jpg</t>
+  </si>
+  <si>
+    <t>13.jpg</t>
+  </si>
+  <si>
+    <t>14.jpg</t>
+  </si>
+  <si>
+    <t>15.jpg</t>
+  </si>
+  <si>
+    <t>16.jpg</t>
+  </si>
+  <si>
+    <t>17.jpg</t>
+  </si>
+  <si>
+    <t>18.jpg</t>
+  </si>
+  <si>
+    <t>19.jpg</t>
+  </si>
+  <si>
+    <t>2.jpg</t>
+  </si>
+  <si>
+    <t>20.jpg</t>
+  </si>
+  <si>
+    <t>3.jpg</t>
+  </si>
+  <si>
+    <t>4.jpg</t>
+  </si>
+  <si>
+    <t>5.jpg</t>
+  </si>
+  <si>
+    <t>6.jpg</t>
+  </si>
+  <si>
+    <t>7.jpg</t>
+  </si>
+  <si>
+    <t>8.jpg</t>
+  </si>
+  <si>
+    <t>9.jpg</t>
+  </si>
+  <si>
+    <t>Is_Detected</t>
+  </si>
+  <si>
+    <t>Letters</t>
+  </si>
+  <si>
+    <t>م ط ر</t>
+  </si>
+  <si>
+    <t>ر س م</t>
+  </si>
+  <si>
+    <t>ر ص و</t>
+  </si>
+  <si>
+    <t>ر ع أ</t>
+  </si>
+  <si>
+    <t>ر س ه</t>
+  </si>
+  <si>
+    <t>ر أ د</t>
+  </si>
+  <si>
+    <t>ر ب ط</t>
+  </si>
+  <si>
+    <t>م ن س</t>
+  </si>
+  <si>
+    <t>م ف</t>
+  </si>
+  <si>
+    <t>ب ط ل</t>
+  </si>
+  <si>
+    <t>ي ي ي</t>
+  </si>
+  <si>
+    <t>و و و</t>
+  </si>
+  <si>
+    <t>م ج د</t>
+  </si>
+  <si>
+    <t>ر ن أ</t>
+  </si>
+  <si>
+    <t>ر ف ي</t>
+  </si>
+  <si>
+    <t>أ ن ج</t>
+  </si>
+  <si>
+    <t>أ ف ط</t>
+  </si>
+  <si>
+    <t>ر س ن</t>
+  </si>
+  <si>
+    <t>ر س أ</t>
+  </si>
+  <si>
+    <t>د ب ج</t>
+  </si>
+  <si>
+    <t>Numbers</t>
+  </si>
+  <si>
+    <t>٥ ٥ ٥</t>
+  </si>
+  <si>
+    <t>٧ ٨ ٩ ٧</t>
+  </si>
+  <si>
+    <t>٤ ٩ ٦ ٧</t>
+  </si>
+  <si>
+    <t>٧ ٧ ٢ ٩</t>
+  </si>
+  <si>
+    <t>٢ ١ ٣ ١</t>
+  </si>
+  <si>
+    <t>٢ ٩ ٥ ٣</t>
+  </si>
+  <si>
+    <t>٥ ٨ ٢ ٨</t>
+  </si>
+  <si>
+    <t>٦ ٦ ٦ ٦</t>
+  </si>
+  <si>
+    <t>١ ١</t>
+  </si>
+  <si>
+    <t>٩ ٥ ٩</t>
+  </si>
+  <si>
+    <t>٩ ٩ ٩</t>
+  </si>
+  <si>
+    <t>٦ ٦ ٦ ٦</t>
+  </si>
+  <si>
+    <t>٤ ٤ ٤</t>
+  </si>
+  <si>
+    <t>٨ ٦ ٤ ٨</t>
+  </si>
+  <si>
+    <t>٤ ٩ ٨ ٧</t>
+  </si>
+  <si>
+    <t>٢ ٣ ٥ ٩</t>
+  </si>
+  <si>
+    <t>٤ ٥ ٩ ٥</t>
+  </si>
+  <si>
+    <t>٥ ١ ٥ ٩</t>
+  </si>
+  <si>
+    <t>٢ ٨ ٩ ٥</t>
+  </si>
+  <si>
+    <t>٩ ٨ ٨ ٧</t>
+  </si>
+  <si>
+    <t>Filename</t>
+  </si>
+  <si>
+    <t>1.jpg</t>
+  </si>
+  <si>
+    <t>10.jpg</t>
+  </si>
+  <si>
+    <t>11.jpg</t>
+  </si>
+  <si>
+    <t>12.jpg</t>
+  </si>
+  <si>
+    <t>13.jpg</t>
+  </si>
+  <si>
+    <t>14.jpg</t>
+  </si>
+  <si>
+    <t>15.jpg</t>
+  </si>
+  <si>
+    <t>16.jpg</t>
+  </si>
+  <si>
+    <t>17.jpg</t>
+  </si>
+  <si>
+    <t>18.jpg</t>
+  </si>
+  <si>
+    <t>19.jpg</t>
+  </si>
+  <si>
+    <t>2.jpg</t>
+  </si>
+  <si>
+    <t>20.jpg</t>
+  </si>
+  <si>
+    <t>3.jpg</t>
+  </si>
+  <si>
+    <t>4.jpg</t>
+  </si>
+  <si>
+    <t>5.jpg</t>
+  </si>
+  <si>
+    <t>6.jpg</t>
+  </si>
+  <si>
+    <t>7.jpg</t>
+  </si>
+  <si>
+    <t>8.jpg</t>
+  </si>
+  <si>
+    <t>9.jpg</t>
+  </si>
+  <si>
+    <t>Is_Detected</t>
+  </si>
+  <si>
+    <t>Letters</t>
+  </si>
+  <si>
+    <t>م ط ر</t>
+  </si>
+  <si>
+    <t>ر س م</t>
+  </si>
+  <si>
+    <t>ر ص و</t>
+  </si>
+  <si>
+    <t>ر ع أ</t>
+  </si>
+  <si>
+    <t>ر س ه</t>
+  </si>
+  <si>
+    <t>ر أ د</t>
+  </si>
+  <si>
+    <t>ر ب ط</t>
+  </si>
+  <si>
+    <t>م ن س</t>
+  </si>
+  <si>
+    <t>م ف</t>
+  </si>
+  <si>
+    <t>ب ط ل</t>
+  </si>
+  <si>
+    <t>ي ي ي</t>
+  </si>
+  <si>
+    <t>و و و</t>
+  </si>
+  <si>
+    <t>م ج د</t>
+  </si>
+  <si>
+    <t>ر ن أ</t>
+  </si>
+  <si>
+    <t>ر ف ي</t>
+  </si>
+  <si>
+    <t>أ ن ج</t>
+  </si>
+  <si>
+    <t>أ ف ط</t>
+  </si>
+  <si>
+    <t>ر س ن</t>
+  </si>
+  <si>
+    <t>ر س أ</t>
+  </si>
+  <si>
+    <t>د ب ج</t>
+  </si>
+  <si>
+    <t>Numbers</t>
+  </si>
+  <si>
+    <t>٥ ٥ ٥</t>
+  </si>
+  <si>
+    <t>٧ ٨ ٩ ٧</t>
+  </si>
+  <si>
+    <t>٤ ٩ ٦ ٧</t>
+  </si>
+  <si>
+    <t>٧ ٧ ٢ ٩</t>
+  </si>
+  <si>
+    <t>٢ ١ ٣ ١</t>
+  </si>
+  <si>
+    <t>٢ ٩ ٥ ٣</t>
+  </si>
+  <si>
+    <t>٥ ٨ ٢ ٨</t>
+  </si>
+  <si>
+    <t>٦ ٦ ٦ ٦</t>
+  </si>
+  <si>
+    <t>١ ١</t>
+  </si>
+  <si>
+    <t>٩ ٥ ٩</t>
+  </si>
+  <si>
+    <t>٩ ٩ ٩</t>
+  </si>
+  <si>
+    <t>٦ ٦ ٦ ٦</t>
+  </si>
+  <si>
+    <t>٤ ٤ ٤</t>
+  </si>
+  <si>
+    <t>٨ ٦ ٤ ٨</t>
+  </si>
+  <si>
+    <t>٤ ٩ ٨ ٧</t>
+  </si>
+  <si>
+    <t>٢ ٣ ٥ ٩</t>
+  </si>
+  <si>
+    <t>٤ ٥ ٩ ٥</t>
+  </si>
+  <si>
+    <t>٥ ١ ٥ ٩</t>
+  </si>
+  <si>
+    <t>٢ ٨ ٩ ٥</t>
   </si>
   <si>
     <t>٩ ٨ ٨ ٧</t>
@@ -435,7 +1203,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="4">
+  <borders count="8">
     <border>
       <left/>
       <right/>
@@ -446,15 +1214,23 @@
     <border/>
     <border/>
     <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="22" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="true"/>
     <xf numFmtId="22" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="true"/>
     <xf numFmtId="22" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="true"/>
+    <xf numFmtId="22" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="true"/>
+    <xf numFmtId="22" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="true"/>
+    <xf numFmtId="22" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="true"/>
+    <xf numFmtId="22" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="true"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -475,296 +1251,296 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="0" t="s">
-        <v>70</v>
+        <v>326</v>
       </c>
       <c r="B1" s="0" t="s">
-        <v>91</v>
+        <v>347</v>
       </c>
       <c r="C1" s="0" t="s">
-        <v>92</v>
+        <v>348</v>
       </c>
       <c r="D1" s="0" t="s">
-        <v>113</v>
+        <v>369</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="0" t="s">
-        <v>71</v>
+        <v>327</v>
       </c>
       <c r="B2" s="0" t="b">
         <v>1</v>
       </c>
       <c r="C2" s="0" t="s">
-        <v>93</v>
+        <v>349</v>
       </c>
       <c r="D2" s="0" t="s">
-        <v>114</v>
+        <v>370</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="0" t="s">
-        <v>72</v>
+        <v>328</v>
       </c>
       <c r="B3" s="0" t="b">
         <v>1</v>
       </c>
       <c r="C3" s="0" t="s">
-        <v>94</v>
+        <v>350</v>
       </c>
       <c r="D3" s="0" t="s">
-        <v>115</v>
+        <v>371</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="0" t="s">
-        <v>73</v>
+        <v>329</v>
       </c>
       <c r="B4" s="0" t="b">
         <v>1</v>
       </c>
       <c r="C4" s="0" t="s">
-        <v>95</v>
+        <v>351</v>
       </c>
       <c r="D4" s="0" t="s">
-        <v>116</v>
+        <v>372</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="0" t="s">
-        <v>74</v>
+        <v>330</v>
       </c>
       <c r="B5" s="0" t="b">
         <v>1</v>
       </c>
       <c r="C5" s="0" t="s">
-        <v>96</v>
+        <v>352</v>
       </c>
       <c r="D5" s="0" t="s">
-        <v>117</v>
+        <v>373</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="0" t="s">
-        <v>75</v>
+        <v>331</v>
       </c>
       <c r="B6" s="0" t="b">
         <v>1</v>
       </c>
       <c r="C6" s="0" t="s">
-        <v>97</v>
+        <v>353</v>
       </c>
       <c r="D6" s="0" t="s">
-        <v>118</v>
+        <v>374</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="0" t="s">
-        <v>76</v>
+        <v>332</v>
       </c>
       <c r="B7" s="0" t="b">
         <v>1</v>
       </c>
       <c r="C7" s="0" t="s">
-        <v>98</v>
+        <v>354</v>
       </c>
       <c r="D7" s="0" t="s">
-        <v>119</v>
+        <v>375</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="0" t="s">
-        <v>77</v>
+        <v>333</v>
       </c>
       <c r="B8" s="0" t="b">
         <v>1</v>
       </c>
       <c r="C8" s="0" t="s">
-        <v>99</v>
+        <v>355</v>
       </c>
       <c r="D8" s="0" t="s">
-        <v>120</v>
+        <v>376</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="0" t="s">
-        <v>78</v>
+        <v>334</v>
       </c>
       <c r="B9" s="0" t="b">
         <v>1</v>
       </c>
       <c r="C9" s="0" t="s">
-        <v>100</v>
+        <v>356</v>
       </c>
       <c r="D9" s="0" t="s">
-        <v>121</v>
+        <v>377</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="0" t="s">
-        <v>79</v>
+        <v>335</v>
       </c>
       <c r="B10" s="0" t="b">
         <v>1</v>
       </c>
       <c r="C10" s="0" t="s">
-        <v>101</v>
+        <v>357</v>
       </c>
       <c r="D10" s="0" t="s">
-        <v>122</v>
+        <v>378</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="0" t="s">
-        <v>80</v>
+        <v>336</v>
       </c>
       <c r="B11" s="0" t="b">
         <v>1</v>
       </c>
       <c r="C11" s="0" t="s">
-        <v>102</v>
+        <v>358</v>
       </c>
       <c r="D11" s="0" t="s">
-        <v>123</v>
+        <v>379</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="0" t="s">
-        <v>81</v>
+        <v>337</v>
       </c>
       <c r="B12" s="0" t="b">
         <v>1</v>
       </c>
       <c r="C12" s="0" t="s">
-        <v>103</v>
+        <v>359</v>
       </c>
       <c r="D12" s="0" t="s">
-        <v>124</v>
+        <v>380</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="0" t="s">
-        <v>82</v>
+        <v>338</v>
       </c>
       <c r="B13" s="0" t="b">
         <v>1</v>
       </c>
       <c r="C13" s="0" t="s">
-        <v>104</v>
+        <v>360</v>
       </c>
       <c r="D13" s="0" t="s">
-        <v>125</v>
+        <v>381</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="0" t="s">
-        <v>83</v>
+        <v>339</v>
       </c>
       <c r="B14" s="0" t="b">
         <v>1</v>
       </c>
       <c r="C14" s="0" t="s">
-        <v>105</v>
+        <v>361</v>
       </c>
       <c r="D14" s="0" t="s">
-        <v>126</v>
+        <v>382</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="0" t="s">
-        <v>84</v>
+        <v>340</v>
       </c>
       <c r="B15" s="0" t="b">
         <v>1</v>
       </c>
       <c r="C15" s="0" t="s">
-        <v>106</v>
+        <v>362</v>
       </c>
       <c r="D15" s="0" t="s">
-        <v>127</v>
+        <v>383</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="0" t="s">
-        <v>85</v>
+        <v>341</v>
       </c>
       <c r="B16" s="0" t="b">
         <v>1</v>
       </c>
       <c r="C16" s="0" t="s">
-        <v>107</v>
+        <v>363</v>
       </c>
       <c r="D16" s="0" t="s">
-        <v>128</v>
+        <v>384</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="0" t="s">
-        <v>86</v>
+        <v>342</v>
       </c>
       <c r="B17" s="0" t="b">
         <v>1</v>
       </c>
       <c r="C17" s="0" t="s">
-        <v>108</v>
+        <v>364</v>
       </c>
       <c r="D17" s="0" t="s">
-        <v>129</v>
+        <v>385</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="0" t="s">
-        <v>87</v>
+        <v>343</v>
       </c>
       <c r="B18" s="0" t="b">
         <v>1</v>
       </c>
       <c r="C18" s="0" t="s">
-        <v>109</v>
+        <v>365</v>
       </c>
       <c r="D18" s="0" t="s">
-        <v>130</v>
+        <v>386</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="0" t="s">
-        <v>88</v>
+        <v>344</v>
       </c>
       <c r="B19" s="0" t="b">
         <v>1</v>
       </c>
       <c r="C19" s="0" t="s">
-        <v>110</v>
+        <v>366</v>
       </c>
       <c r="D19" s="0" t="s">
-        <v>131</v>
+        <v>387</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="0" t="s">
-        <v>89</v>
+        <v>345</v>
       </c>
       <c r="B20" s="0" t="b">
         <v>1</v>
       </c>
       <c r="C20" s="0" t="s">
-        <v>111</v>
+        <v>367</v>
       </c>
       <c r="D20" s="0" t="s">
-        <v>132</v>
+        <v>388</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="0" t="s">
-        <v>90</v>
+        <v>346</v>
       </c>
       <c r="B21" s="0" t="b">
         <v>1</v>
       </c>
       <c r="C21" s="0" t="s">
-        <v>112</v>
+        <v>368</v>
       </c>
       <c r="D21" s="0" t="s">
-        <v>133</v>
+        <v>389</v>
       </c>
     </row>
   </sheetData>
